--- a/docs/03_Safety_Specification/safety_requirements.xlsx
+++ b/docs/03_Safety_Specification/safety_requirements.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>add_product_to_list</t>
+          <t>add_product</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>add_product_to_list</t>
+          <t>add_product</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>import_product_stock</t>
+          <t>import_stock</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>export_product_stock</t>
+          <t>export_stock</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>GUARDED_IN_V0 (Hàm safe_string_copy sử dụng snprintf hoặc vòng lặp kiểm tra bounds nghiêm ngặt)</t>
+          <t>POTENTIAL_RISK_IN_V0 (Baseline v0 dùng strncpy không tự động null-terminate khi chuỗi nguồn dài hơn buffer; được chuẩn hóa an toàn trong bản vá v1)</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>GUARDED_IN_V0 (fgets chỉ định kích thước sizeof(line) = 512)</t>
+          <t>POTENTIAL_RISK_IN_V0 (Baseline v0 chưa kiểm tra ký tự '\n' và thiếu cơ chế drain buffer khi dòng vượt 512B -&gt; Silent Line Truncation CWE-120; được khắc phục trong bản vá v1)</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>add_product_to_list</t>
+          <t>add_product</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>param == NULL -&gt; return STATUS_ERR_NULL_POINTER</t>
+          <t>param == NULL -&gt; return STATUS_ERR_NULL_PTR (-1)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>GUARDED_IN_V0 (100% các hàm API trong baseline v0 đều kiểm tra if (!list) return -2;)</t>
+          <t>GUARDED_IN_V0 (100% các hàm API trong baseline v0 đều kiểm tra if (!list) return -1;)</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>GUARDED_IN_V0 (Có guard `token_count &lt; 8` trong vòng lặp parse)</t>
+          <t>POTENTIAL_RISK_IN_V0 (Baseline v0 khai báo tokens[6] nhưng chưa có guard chặn token_count &lt; 6 -&gt; Nguy cơ Stack Buffer Overflow CWE-121; được khắc phục triệt để trong bản vá v1)</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
